--- a/output/comentarios_procesados.xlsx
+++ b/output/comentarios_procesados.xlsx
@@ -481,7 +481,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -497,7 +497,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -529,7 +529,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -561,7 +561,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -577,7 +577,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
@@ -593,7 +593,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -609,7 +609,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -657,7 +657,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -673,7 +673,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -705,7 +705,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -737,7 +737,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -753,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23">
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -833,7 +833,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -849,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
@@ -881,7 +881,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30">
@@ -961,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -977,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -993,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1041,7 +1041,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1073,7 +1073,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41">
@@ -1121,7 +1121,7 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1169,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47">
@@ -1185,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1217,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51">
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
@@ -1297,7 +1297,7 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1313,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1361,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59">
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60">
@@ -1393,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1457,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1537,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="70">
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -1569,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1601,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1617,7 +1617,7 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75">
@@ -1633,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1665,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1745,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -1777,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1793,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="86">
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -1873,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -1889,7 +1889,7 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1905,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1937,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -1953,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1985,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -2001,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2017,7 +2017,7 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2033,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="101">
@@ -2049,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2065,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2081,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2097,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2129,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -2161,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2209,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2225,7 +2225,7 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="113">
@@ -2257,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="115">
@@ -2273,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2289,7 +2289,7 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -2305,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -2321,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2337,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -2385,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="123">
@@ -2401,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -2417,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="125">
@@ -2465,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -2497,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -2513,7 +2513,7 @@
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="131">
@@ -2529,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -2561,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -2577,7 +2577,7 @@
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -2593,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="136">
@@ -2657,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -2673,7 +2673,7 @@
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -2705,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="143">
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -2769,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -2817,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -2849,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -2865,7 +2865,7 @@
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="153">
@@ -2897,7 +2897,7 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -2929,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="157">
@@ -3025,7 +3025,7 @@
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -3041,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -3057,7 +3057,7 @@
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="165">
@@ -3089,7 +3089,7 @@
         <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -3105,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -3121,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -3137,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -3153,7 +3153,7 @@
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -3169,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -3185,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -3201,7 +3201,7 @@
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="174">
@@ -3249,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -3265,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -3297,7 +3297,7 @@
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="180">
@@ -3313,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -3345,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="183">
@@ -3377,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -3393,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -3409,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="187">
@@ -3441,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -3457,7 +3457,7 @@
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="191">
@@ -3489,7 +3489,7 @@
         <v>1</v>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="192">
@@ -3521,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -3537,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="195">
@@ -3553,7 +3553,7 @@
         <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="196">
@@ -3569,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197">
@@ -3585,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -3617,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="D199" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -3633,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="201">
@@ -3701,7 +3701,7 @@
         <v>-1</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3765,7 +3765,7 @@
         <v>-1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3781,7 +3781,7 @@
         <v>-1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3797,7 +3797,7 @@
         <v>-1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3813,7 +3813,7 @@
         <v>-1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
@@ -3845,7 +3845,7 @@
         <v>-1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3861,7 +3861,7 @@
         <v>-1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
@@ -3893,7 +3893,7 @@
         <v>-1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3925,7 +3925,7 @@
         <v>-1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17">
@@ -3957,7 +3957,7 @@
         <v>-1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
@@ -3973,7 +3973,7 @@
         <v>-1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -3989,7 +3989,7 @@
         <v>-1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4005,7 +4005,7 @@
         <v>-1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
@@ -4037,7 +4037,7 @@
         <v>-1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24">
@@ -4069,7 +4069,7 @@
         <v>-1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -4085,7 +4085,7 @@
         <v>-1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
@@ -4101,7 +4101,7 @@
         <v>-1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="28">
@@ -4117,7 +4117,7 @@
         <v>-1</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
@@ -4133,7 +4133,7 @@
         <v>-1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -4149,7 +4149,7 @@
         <v>-1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4165,7 +4165,7 @@
         <v>-1</v>
       </c>
       <c r="D31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4181,7 +4181,7 @@
         <v>-1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -4197,7 +4197,7 @@
         <v>-1</v>
       </c>
       <c r="D33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4213,7 +4213,7 @@
         <v>-1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4229,7 +4229,7 @@
         <v>-1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -4245,7 +4245,7 @@
         <v>-1</v>
       </c>
       <c r="D36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4277,7 +4277,7 @@
         <v>-1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39">
@@ -4293,7 +4293,7 @@
         <v>-1</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40">
@@ -4309,7 +4309,7 @@
         <v>-1</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41">
@@ -4357,7 +4357,7 @@
         <v>-1</v>
       </c>
       <c r="D43" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4373,7 +4373,7 @@
         <v>-1</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -4389,7 +4389,7 @@
         <v>-1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46">
@@ -4405,7 +4405,7 @@
         <v>-1</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47">
@@ -4421,7 +4421,7 @@
         <v>-1</v>
       </c>
       <c r="D47" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4485,7 +4485,7 @@
         <v>-1</v>
       </c>
       <c r="D51" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4501,7 +4501,7 @@
         <v>-1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4517,7 +4517,7 @@
         <v>-1</v>
       </c>
       <c r="D53" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4533,7 +4533,7 @@
         <v>-1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4549,7 +4549,7 @@
         <v>-1</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -4597,7 +4597,7 @@
         <v>-1</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59">
@@ -4613,7 +4613,7 @@
         <v>-1</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60">
@@ -4629,7 +4629,7 @@
         <v>-1</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
@@ -4645,7 +4645,7 @@
         <v>-1</v>
       </c>
       <c r="D61" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4661,7 +4661,7 @@
         <v>-1</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63">
@@ -4693,7 +4693,7 @@
         <v>-1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65">
@@ -4709,7 +4709,7 @@
         <v>-1</v>
       </c>
       <c r="D65" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4725,7 +4725,7 @@
         <v>-1</v>
       </c>
       <c r="D66" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4741,7 +4741,7 @@
         <v>-1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4773,7 +4773,7 @@
         <v>-1</v>
       </c>
       <c r="D69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4789,7 +4789,7 @@
         <v>-1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="71">
@@ -4805,7 +4805,7 @@
         <v>-1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="72">
@@ -4821,7 +4821,7 @@
         <v>-1</v>
       </c>
       <c r="D72" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4853,7 +4853,7 @@
         <v>-1</v>
       </c>
       <c r="D74" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4869,7 +4869,7 @@
         <v>-1</v>
       </c>
       <c r="D75" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4917,7 +4917,7 @@
         <v>-1</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4949,7 +4949,7 @@
         <v>-1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="81">
@@ -4981,7 +4981,7 @@
         <v>-1</v>
       </c>
       <c r="D82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5013,7 +5013,7 @@
         <v>-1</v>
       </c>
       <c r="D84" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5029,7 +5029,7 @@
         <v>-1</v>
       </c>
       <c r="D85" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5045,7 +5045,7 @@
         <v>-1</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5061,7 +5061,7 @@
         <v>-1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5109,7 +5109,7 @@
         <v>-1</v>
       </c>
       <c r="D90" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5141,7 +5141,7 @@
         <v>-1</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5205,7 +5205,7 @@
         <v>-1</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="97">
@@ -5221,7 +5221,7 @@
         <v>-1</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -5237,7 +5237,7 @@
         <v>-1</v>
       </c>
       <c r="D98" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -5253,7 +5253,7 @@
         <v>-1</v>
       </c>
       <c r="D99" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -5301,7 +5301,7 @@
         <v>-1</v>
       </c>
       <c r="D102" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5349,7 +5349,7 @@
         <v>-1</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -5397,7 +5397,7 @@
         <v>-1</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="109">
@@ -5445,7 +5445,7 @@
         <v>-1</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="112">
@@ -5461,7 +5461,7 @@
         <v>-1</v>
       </c>
       <c r="D112" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5477,7 +5477,7 @@
         <v>-1</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -5493,7 +5493,7 @@
         <v>-1</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -5525,7 +5525,7 @@
         <v>-1</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="117">
@@ -5541,7 +5541,7 @@
         <v>-1</v>
       </c>
       <c r="D117" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5557,7 +5557,7 @@
         <v>-1</v>
       </c>
       <c r="D118" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -5573,7 +5573,7 @@
         <v>-1</v>
       </c>
       <c r="D119" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -5589,7 +5589,7 @@
         <v>-1</v>
       </c>
       <c r="D120" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -5637,7 +5637,7 @@
         <v>-1</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="124">
@@ -5685,7 +5685,7 @@
         <v>-1</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="127">
@@ -5701,7 +5701,7 @@
         <v>-1</v>
       </c>
       <c r="D127" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -5717,7 +5717,7 @@
         <v>-1</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -5733,7 +5733,7 @@
         <v>-1</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -5749,7 +5749,7 @@
         <v>-1</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="131">
@@ -5797,7 +5797,7 @@
         <v>-1</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -5829,7 +5829,7 @@
         <v>-1</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -5845,7 +5845,7 @@
         <v>-1</v>
       </c>
       <c r="D136" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -5877,7 +5877,7 @@
         <v>-1</v>
       </c>
       <c r="D138" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -5925,7 +5925,7 @@
         <v>-1</v>
       </c>
       <c r="D141" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -5941,7 +5941,7 @@
         <v>-1</v>
       </c>
       <c r="D142" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -5957,7 +5957,7 @@
         <v>-1</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="144">
@@ -5973,7 +5973,7 @@
         <v>-1</v>
       </c>
       <c r="D144" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -5989,7 +5989,7 @@
         <v>-1</v>
       </c>
       <c r="D145" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -6005,7 +6005,7 @@
         <v>-1</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="147">
@@ -6037,7 +6037,7 @@
         <v>-1</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -6053,7 +6053,7 @@
         <v>-1</v>
       </c>
       <c r="D149" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -6069,7 +6069,7 @@
         <v>-1</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="151">
@@ -6085,7 +6085,7 @@
         <v>-1</v>
       </c>
       <c r="D151" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6101,7 +6101,7 @@
         <v>-1</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="153">
@@ -6117,7 +6117,7 @@
         <v>-1</v>
       </c>
       <c r="D153" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -6149,7 +6149,7 @@
         <v>-1</v>
       </c>
       <c r="D155" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -6165,7 +6165,7 @@
         <v>-1</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="157">
@@ -6181,7 +6181,7 @@
         <v>-1</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="158">
@@ -6197,7 +6197,7 @@
         <v>-1</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -6229,7 +6229,7 @@
         <v>-1</v>
       </c>
       <c r="D160" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -6277,7 +6277,7 @@
         <v>-1</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -6293,7 +6293,7 @@
         <v>-1</v>
       </c>
       <c r="D164" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -6309,7 +6309,7 @@
         <v>-1</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -6325,7 +6325,7 @@
         <v>-1</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -6357,7 +6357,7 @@
         <v>-1</v>
       </c>
       <c r="D168" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -6373,7 +6373,7 @@
         <v>-1</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -6389,7 +6389,7 @@
         <v>-1</v>
       </c>
       <c r="D170" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -6405,7 +6405,7 @@
         <v>-1</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="172">
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="D174" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -6485,7 +6485,7 @@
         <v>-1</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -6501,7 +6501,7 @@
         <v>-1</v>
       </c>
       <c r="D177" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -6533,7 +6533,7 @@
         <v>-1</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -6645,7 +6645,7 @@
         <v>-1</v>
       </c>
       <c r="D186" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -6677,7 +6677,7 @@
         <v>-1</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -6693,7 +6693,7 @@
         <v>-1</v>
       </c>
       <c r="D189" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -6709,7 +6709,7 @@
         <v>-1</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="191">
@@ -6741,7 +6741,7 @@
         <v>-1</v>
       </c>
       <c r="D192" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -6757,7 +6757,7 @@
         <v>-1</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -6773,7 +6773,7 @@
         <v>-1</v>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -6789,7 +6789,7 @@
         <v>-1</v>
       </c>
       <c r="D195" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -6805,7 +6805,7 @@
         <v>-1</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197">
@@ -6837,7 +6837,7 @@
         <v>-1</v>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -6937,7 +6937,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -6969,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -6985,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7001,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7017,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -7065,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -7081,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7097,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7113,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7129,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
@@ -7161,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -7177,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
@@ -7193,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
@@ -7209,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21">
@@ -7241,7 +7241,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
@@ -7257,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -7273,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -7289,7 +7289,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
@@ -7305,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26">
@@ -7337,7 +7337,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="31">
@@ -7401,7 +7401,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -7417,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -7433,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -7449,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -7465,7 +7465,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36">
@@ -7481,7 +7481,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -7513,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -7545,7 +7545,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -7561,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42">
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -7593,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -7609,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -7625,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -7657,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
@@ -7673,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7689,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -7737,7 +7737,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -7753,7 +7753,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -7769,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="55">
@@ -7785,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -7801,7 +7801,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -7817,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -7849,7 +7849,7 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60">
@@ -7865,7 +7865,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
@@ -7881,7 +7881,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="64">
@@ -7929,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -7945,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -7977,7 +7977,7 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68">
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69">
@@ -8025,7 +8025,7 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -8041,7 +8041,7 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -8121,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77">
@@ -8137,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -8153,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="79">
@@ -8185,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -8201,7 +8201,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -8217,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -8233,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -8249,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="85">
@@ -8265,7 +8265,7 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -8313,7 +8313,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -8329,7 +8329,7 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="90">
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -8377,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -8393,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="94">
@@ -8425,7 +8425,7 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -8473,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -8537,7 +8537,7 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="103">
@@ -8553,7 +8553,7 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="104">
@@ -8569,7 +8569,7 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -8585,7 +8585,7 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -8601,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -8649,7 +8649,7 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -8681,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -8697,7 +8697,7 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="113">
@@ -8713,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -8729,7 +8729,7 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -8761,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -8793,7 +8793,7 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -8809,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -8825,7 +8825,7 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -8857,7 +8857,7 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -8873,7 +8873,7 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -8905,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="126">
@@ -8921,7 +8921,7 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -8953,7 +8953,7 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -8969,7 +8969,7 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -8985,7 +8985,7 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="131">
@@ -9001,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -9017,7 +9017,7 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -9033,7 +9033,7 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="134">
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="135">
@@ -9065,7 +9065,7 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -9081,7 +9081,7 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="137">
@@ -9113,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -9145,7 +9145,7 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -9161,7 +9161,7 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="142">
@@ -9177,7 +9177,7 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="143">
@@ -9193,7 +9193,7 @@
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -9209,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="145">
@@ -9225,7 +9225,7 @@
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="146">
@@ -9241,7 +9241,7 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -9257,7 +9257,7 @@
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="148">
@@ -9289,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -9321,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -9337,7 +9337,7 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -9385,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -9449,7 +9449,7 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -9497,7 +9497,7 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="163">
@@ -9513,7 +9513,7 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="164">
@@ -9545,7 +9545,7 @@
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -9561,7 +9561,7 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="167">
@@ -9577,7 +9577,7 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -9641,7 +9641,7 @@
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="172">
@@ -9673,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -9705,7 +9705,7 @@
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -9721,7 +9721,7 @@
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -9737,7 +9737,7 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="178">
@@ -9753,7 +9753,7 @@
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -9769,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -9785,7 +9785,7 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="181">
@@ -9817,7 +9817,7 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="183">
@@ -9833,7 +9833,7 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="185">
@@ -9865,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="187">
@@ -9897,7 +9897,7 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -9929,7 +9929,7 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -9945,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -9961,7 +9961,7 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -9977,7 +9977,7 @@
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -10009,7 +10009,7 @@
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -10041,7 +10041,7 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197">
@@ -10057,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -10073,7 +10073,7 @@
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -10105,7 +10105,7 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="201">
@@ -10121,7 +10121,7 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/output/comentarios_procesados.xlsx
+++ b/output/comentarios_procesados.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="positivos " sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="negativos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="neutro" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,7 +480,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -497,7 +496,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +512,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -577,7 +576,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -625,7 +624,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -641,7 +640,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -657,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -673,7 +672,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -689,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -721,7 +720,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -769,7 +768,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -817,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -849,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -865,7 +864,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -881,7 +880,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -897,7 +896,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -913,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -929,7 +928,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -945,7 +944,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -961,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -977,7 +976,7 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -993,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1009,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1025,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1041,7 +1040,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1057,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1073,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1089,7 +1088,7 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1105,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1169,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1217,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1233,7 +1232,7 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1249,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1281,7 +1280,7 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1329,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1361,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1377,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1425,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1441,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -1457,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1473,7 +1472,7 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1489,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1505,7 +1504,7 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -1521,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -1537,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -1585,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -1601,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -1617,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1633,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -1681,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -1729,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -1793,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -1825,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -1889,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -1905,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -1921,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -1953,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -2017,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2033,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2049,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2065,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2097,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2145,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -2161,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -2193,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -2209,7 +2208,7 @@
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -2225,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -2241,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -2257,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -2273,7 +2272,7 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -2321,7 +2320,7 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -2337,7 +2336,7 @@
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -2369,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -2385,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -2417,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -2433,7 +2432,7 @@
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -2481,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -2497,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -2513,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -2593,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -2625,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -2705,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -2721,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -2737,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -2785,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -2801,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -2849,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -2865,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -2897,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -2929,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -2977,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -2993,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -3009,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -3041,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -3057,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -3073,7 +3072,7 @@
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -3105,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -3121,7 +3120,7 @@
         <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -3153,7 +3152,7 @@
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -3169,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -3201,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -3217,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -3233,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -3249,7 +3248,7 @@
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -3265,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -3281,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -3297,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -3313,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -3329,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -3345,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -3377,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -3409,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -3457,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -3473,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -3489,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="D191" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -3505,7 +3504,7 @@
         <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -3537,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -3553,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -3569,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -3585,7 +3584,7 @@
         <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -3601,7 +3600,7 @@
         <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -3617,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -3633,7 +3632,7 @@
         <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -3649,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3698,10 +3697,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3714,10 +3713,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3730,7 +3729,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3746,10 +3745,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3762,7 +3761,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -3778,10 +3777,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3794,7 +3793,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3810,10 +3809,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3826,10 +3825,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3842,7 +3841,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -3858,10 +3857,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3874,10 +3873,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3890,10 +3889,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3906,7 +3905,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3922,10 +3921,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3938,10 +3937,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3954,10 +3953,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3970,10 +3969,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3986,10 +3985,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4002,10 +4001,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -4018,10 +4017,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4034,10 +4033,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4050,10 +4049,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4066,7 +4065,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -4082,10 +4081,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4098,10 +4097,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4114,10 +4113,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4130,7 +4129,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -4146,7 +4145,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -4162,7 +4161,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -4178,10 +4177,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4194,7 +4193,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -4210,7 +4209,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -4226,10 +4225,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4242,10 +4241,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4258,10 +4257,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4274,10 +4273,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4290,10 +4289,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4306,10 +4305,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4322,10 +4321,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -4338,7 +4337,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -4354,7 +4353,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -4370,10 +4369,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4386,10 +4385,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4402,10 +4401,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4418,10 +4417,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4434,7 +4433,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -4450,7 +4449,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -4466,10 +4465,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4482,10 +4481,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4498,7 +4497,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -4514,7 +4513,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -4530,7 +4529,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -4546,10 +4545,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4562,10 +4561,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4578,10 +4577,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4594,10 +4593,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4610,10 +4609,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4626,10 +4625,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4642,7 +4641,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -4658,10 +4657,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4674,7 +4673,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -4690,10 +4689,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4706,7 +4705,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -4722,7 +4721,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
@@ -4738,7 +4737,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -4754,7 +4753,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -4770,7 +4769,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
@@ -4786,10 +4785,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4802,10 +4801,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4818,7 +4817,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -4834,10 +4833,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4850,10 +4849,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4866,7 +4865,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -4882,10 +4881,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4898,10 +4897,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4914,7 +4913,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -4930,10 +4929,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4946,10 +4945,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4962,7 +4961,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -4978,7 +4977,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -4994,7 +4993,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -5010,10 +5009,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5026,7 +5025,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
@@ -5042,10 +5041,10 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5058,7 +5057,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -5074,10 +5073,10 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5090,10 +5089,10 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5106,10 +5105,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5122,10 +5121,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -5138,10 +5137,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5154,7 +5153,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -5170,10 +5169,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5186,10 +5185,10 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5202,10 +5201,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5218,10 +5217,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5234,10 +5233,10 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5250,10 +5249,10 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5266,7 +5265,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -5282,7 +5281,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -5298,7 +5297,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -5314,10 +5313,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5330,10 +5329,10 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -5346,7 +5345,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -5362,7 +5361,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -5378,10 +5377,10 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -5394,10 +5393,10 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -5410,7 +5409,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -5426,7 +5425,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
@@ -5442,10 +5441,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -5458,7 +5457,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -5474,7 +5473,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -5490,7 +5489,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
@@ -5506,10 +5505,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5522,10 +5521,10 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5538,7 +5537,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -5554,10 +5553,10 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5570,10 +5569,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5586,7 +5585,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -5602,10 +5601,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -5618,7 +5617,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -5634,10 +5633,10 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -5650,10 +5649,10 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5666,10 +5665,10 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5682,10 +5681,10 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5698,10 +5697,10 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -5714,10 +5713,10 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5730,10 +5729,10 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5746,10 +5745,10 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5762,10 +5761,10 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5778,10 +5777,10 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -5794,7 +5793,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -5810,7 +5809,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -5826,7 +5825,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -5842,10 +5841,10 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -5858,10 +5857,10 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -5874,7 +5873,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -5890,10 +5889,10 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -5906,10 +5905,10 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -5922,10 +5921,10 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -5938,7 +5937,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -5954,10 +5953,10 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -5970,7 +5969,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -5986,10 +5985,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6002,10 +6001,10 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -6018,7 +6017,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -6034,10 +6033,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -6050,10 +6049,10 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -6066,10 +6065,10 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -6082,7 +6081,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -6098,10 +6097,10 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -6114,10 +6113,10 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -6130,10 +6129,10 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -6146,7 +6145,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
@@ -6162,10 +6161,10 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -6178,10 +6177,10 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -6194,7 +6193,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -6210,7 +6209,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -6226,7 +6225,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
         <v>1</v>
@@ -6242,10 +6241,10 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -6258,10 +6257,10 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -6274,7 +6273,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -6290,7 +6289,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -6306,10 +6305,10 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -6322,7 +6321,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -6338,7 +6337,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -6354,7 +6353,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -6370,7 +6369,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -6386,10 +6385,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -6402,10 +6401,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -6418,10 +6417,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -6434,10 +6433,10 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -6450,7 +6449,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -6466,10 +6465,10 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -6482,10 +6481,10 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -6498,7 +6497,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -6514,10 +6513,10 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -6530,10 +6529,10 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -6546,10 +6545,10 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -6562,7 +6561,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -6578,7 +6577,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -6594,10 +6593,10 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -6610,10 +6609,10 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -6626,10 +6625,10 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -6642,7 +6641,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -6658,10 +6657,10 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -6674,10 +6673,10 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -6690,10 +6689,10 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -6706,10 +6705,10 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -6722,10 +6721,10 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -6738,10 +6737,10 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -6754,10 +6753,10 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -6770,10 +6769,10 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -6786,7 +6785,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
         <v>1</v>
@@ -6802,10 +6801,10 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -6818,10 +6817,10 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -6834,7 +6833,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
         <v>0</v>
@@ -6850,10 +6849,10 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -6866,10 +6865,10 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -6882,3246 +6881,10 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D201"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Comentario</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Codigo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>inferencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Funciona como se espera.</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Cumple lo básico, sin más.</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Normal, nada fuera de lo común.</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Está bien, sin destacar.</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Resultado estándar, esperado.</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Funciona, pero nada especial.</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Todo correcto, sin sorpresas.</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Es lo que promete.</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Servicio normal, sin problemas.</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Cumple, pero hasta ahí.</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Está ok, nada más.</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Funciona de manera regular.</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Resultado promedio.</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Nada que comentar, funciona.</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Servicio estándar.</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Correcto, sin destacar.</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Funciona como corresponde.</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Normalito, cumple.</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Todo dentro de lo esperado.</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Sin errores visibles.</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Es funcional.</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Servicio común y corriente.</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Funciona sin mayores cambios.</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Está aceptable.</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Resultado normal.</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Nada fuera de lo esperado.</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Funciona igual que otros.</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Es correcto.</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Servicio básico.</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Cumple su función.</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Está bien hecho, sin destacar.</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Funciona normalmente.</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Todo ok, estándar.</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Resultado neutro.</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Nada especial que mencionar.</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Servicio regular.</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Cumple con lo mínimo.</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Funciona sin fallas notorias.</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Normal, nada raro.</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Está correcto.</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Servicio sin novedades.</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Funciona como siempre.</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Resultado esperado.</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Todo normal.</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Sin cambios relevantes.</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Es funcional, nada más.</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Cumple lo prometido.</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Servicio estándar.</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nada que destacar.</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Funciona adecuadamente.</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Está dentro de lo normal.</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Correcto, sin comentarios.</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Resultado común.</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Funciona sin inconvenientes.</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Todo en orden.</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Servicio promedio.</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Cumple, sin más.</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Está bien, normal.</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Funciona igual que antes.</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Nada fuera de lo común.</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Servicio correcto.</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Resultado estándar.</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Funciona según lo esperado.</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Todo regular.</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Es aceptable.</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Funciona, punto.</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Servicio simple.</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Nada especial.</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Resultado sin variaciones.</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Está ok.</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Cumple lo básico.</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Servicio funcional.</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Funciona normal.</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Resultado habitual.</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Todo correcto.</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Sin observaciones.</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Servicio común.</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Funciona como corresponde.</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Normalito.</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Nada relevante.</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Está dentro del promedio.</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Servicio regular.</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Resultado sin cambios.</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Funciona correctamente.</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Cumple sin destacar.</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Todo normal, ok.</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Servicio estándar.</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Nada fuera de lugar.</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Funciona bien, normal.</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Resultado esperado.</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Servicio sin problemas.</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Funciona tal cual.</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Está bien, promedio.</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Nada que decir.</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Cumple lo justo.</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Servicio neutro.</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Funciona sin novedad.</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Resultado común y corriente.</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Todo en regla.</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Normal.</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Funciona correctamente, estándar.</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Servicio básico.</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Cumple lo mínimo esperado.</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Está bien, nada más.</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Resultado habitual.</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Funciona sin cambios.</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Todo correcto, normal.</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Servicio promedio.</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Nada destacable.</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Funciona y ya.</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Está dentro de lo esperado.</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Servicio común.</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Resultado estándar.</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Funciona bien, sin más.</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Todo normal, correcto.</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Cumple con su función.</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Servicio regular.</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Nada fuera de lo normal.</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Funciona adecuadamente.</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Resultado aceptable.</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Está ok, cumple.</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Servicio funcional.</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Resultado promedio.</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Funciona como siempre.</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Todo dentro de lo normal.</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Servicio estándar.</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Nada especial que decir.</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Funciona correctamente.</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Resultado neutro.</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Está bien, normalito.</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Cumple lo prometido.</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Servicio común y corriente.</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Funciona sin errores aparentes.</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Todo normal.</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Resultado esperado.</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Servicio básico.</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Nada destacable.</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Funciona como debería.</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Está correcto, sin más.</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Servicio regular.</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Resultado habitual.</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Funciona bien, estándar.</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Todo correcto, promedio.</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Cumple su propósito.</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Servicio neutro.</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Nada fuera de lo común.</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Funciona adecuadamente.</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Está ok, normal.</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Resultado sin sorpresas.</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Servicio común.</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Funciona correctamente, normal.</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Todo en orden.</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Resultado estándar.</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Cumple, sin comentarios.</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Servicio regular.</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Nada relevante.</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Funciona como esperado.</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>0</v>
-      </c>
-      <c r="D158" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Está bien, promedio.</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Servicio básico.</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Resultado común.</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Funciona sin problemas.</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Todo normal, estándar.</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Cumple lo justo.</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>0</v>
-      </c>
-      <c r="D164" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Servicio funcional.</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>165</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Resultado neutro.</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Nada especial.</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>0</v>
-      </c>
-      <c r="D167" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Funciona bien, normalito.</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Servicio promedio.</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>0</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Todo correcto.</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>0</v>
-      </c>
-      <c r="D170" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Resultado esperado.</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Funciona correctamente.</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Servicio común.</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Está bien, sin destacar.</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Resultado habitual.</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Cumple su función.</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>0</v>
-      </c>
-      <c r="D176" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Todo normal, ok.</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>0</v>
-      </c>
-      <c r="D177" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Servicio estándar.</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>0</v>
-      </c>
-      <c r="D178" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Funciona como corresponde.</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>0</v>
-      </c>
-      <c r="D179" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Nada fuera de lo normal.</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>0</v>
-      </c>
-      <c r="D180" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Resultado aceptable.</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>0</v>
-      </c>
-      <c r="D181" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Funciona normal.</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>0</v>
-      </c>
-      <c r="D182" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Servicio regular.</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>0</v>
-      </c>
-      <c r="D183" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Está correcto.</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Resultado promedio.</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>0</v>
-      </c>
-      <c r="D185" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Cumple, sin más.</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>0</v>
-      </c>
-      <c r="D186" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Todo dentro del promedio.</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>0</v>
-      </c>
-      <c r="D187" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Servicio común y corriente.</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>0</v>
-      </c>
-      <c r="D188" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Funciona sin novedad.</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>0</v>
-      </c>
-      <c r="D189" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Resultado estándar.</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>0</v>
-      </c>
-      <c r="D190" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Está ok.</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>0</v>
-      </c>
-      <c r="D191" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Funciona como se espera.</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>0</v>
-      </c>
-      <c r="D192" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Servicio básico.</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>0</v>
-      </c>
-      <c r="D193" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Todo normal.</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>0</v>
-      </c>
-      <c r="D194" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Resultado sin cambios.</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>0</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Cumple lo prometido.</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>0</v>
-      </c>
-      <c r="D196" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Servicio neutro.</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>0</v>
-      </c>
-      <c r="D197" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Funciona correctamente, promedio.</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>0</v>
-      </c>
-      <c r="D198" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Nada destacable.</t>
-        </is>
-      </c>
-      <c r="C199" t="n">
-        <v>0</v>
-      </c>
-      <c r="D199" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Resultado esperado.</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>0</v>
-      </c>
-      <c r="D200" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Servicio estándar.</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
-        <v>0</v>
-      </c>
-      <c r="D201" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
